--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486724_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486724_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3527</v>
+        <v>2.8493</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0918</v>
+        <v>4.8367</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7391</v>
+        <v>-1.9874</v>
       </c>
       <c r="G2" t="n">
         <v>1.3527</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1585</v>
+        <v>0.6551</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7718</v>
+        <v>0.5168</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3866</v>
+        <v>0.1383</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.266</v>
+        <v>2.7308</v>
       </c>
       <c r="E3" t="n">
-        <v>3.387</v>
+        <v>3.7525</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.121</v>
+        <v>-1.0217</v>
       </c>
       <c r="G3" t="n">
         <v>2.9597</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.458</v>
+        <v>0.0068</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6623</v>
+        <v>-0.2969</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2044</v>
+        <v>0.3037</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0426</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1505</v>
+        <v>1.1478</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9899</v>
+        <v>3.8383</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8394</v>
+        <v>-2.6904</v>
       </c>
       <c r="G4" t="n">
         <v>0.0281</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2922</v>
+        <v>0.2895</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3307</v>
+        <v>0.1791</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0386</v>
+        <v>0.1104</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3282</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>P. VIVAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6876</v>
+        <v>-0.8354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3616</v>
+        <v>-0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0492</v>
+        <v>-0.6553</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9009</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4894</v>
+        <v>-0.4829</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3903</v>
+        <v>-0.2283</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2516</v>
+        <v>0.0407</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3864</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1348</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1525</v>
+        <v>-0.7519</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.897</v>
+        <v>-0.4829</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2555</v>
+        <v>-0.269</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>0.182</v>
+        <v>-0.3172</v>
       </c>
       <c r="T5" t="n">
-        <v>0.11</v>
+        <v>-0.2207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. VIVAS FERNANDEZ</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8602</v>
+        <v>-0.9756</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.18</v>
+        <v>0.1172</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6802</v>
+        <v>-1.0928</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.4487</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4829</v>
+        <v>-0.9106</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2283</v>
+        <v>-0.5381</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0407</v>
+        <v>0.1242</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7519</v>
+        <v>-1.5728</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4829</v>
+        <v>-1.0348</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.269</v>
+        <v>-0.5381</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3421</v>
+        <v>-0.4344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2207</v>
+        <v>-0.0069</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1213</v>
+        <v>-0.4274</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1535</v>
+        <v>-1.0972</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0138</v>
+        <v>0.0513</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1673</v>
+        <v>-1.1485</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4487</v>
+        <v>-0.9009</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9106</v>
+        <v>0.4894</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5381</v>
+        <v>-1.3903</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1242</v>
+        <v>0.2516</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1242</v>
+        <v>1.3864</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.1348</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5728</v>
+        <v>-1.1525</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0348</v>
+        <v>-0.897</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5381</v>
+        <v>-0.2555</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6123</v>
+        <v>-0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1104</v>
+        <v>-0.2003</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5019</v>
+        <v>-0.0273</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3282</v>
+        <v>-1.5133</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3282</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0377</v>
+        <v>-2.0296</v>
       </c>
       <c r="E8" t="n">
-        <v>0.978</v>
+        <v>1.1849</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0158</v>
+        <v>-3.2144</v>
       </c>
       <c r="G8" t="n">
         <v>1.0329</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0332</v>
+        <v>0.0414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3863</v>
+        <v>-0.1794</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4195</v>
+        <v>0.2208</v>
       </c>
       <c r="V8" t="n">
         <v>-3.6831</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0624</v>
+        <v>-2.1186</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1426</v>
+        <v>-2.7389</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9198</v>
+        <v>0.6203</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0679</v>
+        <v>-1.5393</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7794</v>
+        <v>-1.3584</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2885</v>
+        <v>-0.1809</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7194</v>
+        <v>-1.2769</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6696</v>
+        <v>-1.3583</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0498</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7873</v>
+        <v>-0.2624</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4489</v>
+        <v>-0.0002</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3384</v>
+        <v>-0.2623</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7778</v>
+        <v>-0.3862</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1936</v>
+        <v>-0.4966</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1225</v>
+        <v>-2.2059</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2621</v>
+        <v>-1.0874</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3846</v>
+        <v>-1.1184</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1205</v>
+        <v>-2.0679</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.2403</v>
+        <v>-0.7794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1198</v>
+        <v>-1.2885</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9839</v>
+        <v>0.7194</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.481</v>
+        <v>0.6696</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4649</v>
+        <v>0.0498</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.1045</v>
+        <v>-2.7873</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.7593</v>
+        <v>-1.4489</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3451</v>
+        <v>-1.3384</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7377</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8162</v>
+        <v>0.6343</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9926</v>
+        <v>-0.1384</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1763</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5559</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8415</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2676</v>
+        <v>-2.4355</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7389</v>
+        <v>1.8002</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4713</v>
+        <v>-4.2356</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5393</v>
+        <v>-3.1205</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3584</v>
+        <v>-3.2403</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1809</v>
+        <v>0.1198</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2769</v>
+        <v>0.9839</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3583</v>
+        <v>-0.481</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0814</v>
+        <v>1.4649</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2624</v>
+        <v>-4.1045</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0002</v>
+        <v>-2.7593</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2623</v>
+        <v>-1.3451</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5352</v>
+        <v>0.5033</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>0.5306</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0386</v>
+        <v>-0.0274</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5559</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4722</v>
+        <v>-2.8061</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2707</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7429</v>
+        <v>-3.5939</v>
       </c>
       <c r="G12" t="n">
         <v>-0.591</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0316</v>
+        <v>-0.3655</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4415</v>
+        <v>0.0757</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4412</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2703</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5585</v>
+        <v>-3.4014</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4547</v>
+        <v>-2.2479</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1038</v>
+        <v>-1.1535</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9239</v>
@@ -1468,13 +1468,13 @@
         <v>0.1931</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0055</v>
+        <v>0.1517</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1104</v>
+        <v>0.0965</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1049</v>
+        <v>0.0552</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8568</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.453</v>
+        <v>-11.1774</v>
       </c>
       <c r="E14" t="n">
-        <v>9.838699999999999</v>
+        <v>10.1147</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.2918</v>
+        <v>-21.2916</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.93</v>
+        <v>-6.929999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-8.275300000000001</v>
@@ -1522,7 +1522,7 @@
         <v>18.2847</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2124</v>
+        <v>6.212400000000001</v>
       </c>
       <c r="L14" t="n">
         <v>12.0723</v>
@@ -1546,13 +1546,13 @@
         <v>14.4808</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2752000000000004</v>
+        <v>0.5511999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4167</v>
+        <v>-0.1405</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6918000000000001</v>
+        <v>0.6917000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-7.6943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1713</v>
+        <v>3.2762</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1669</v>
+        <v>5.96</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9956</v>
+        <v>-2.6838</v>
       </c>
       <c r="G15" t="n">
         <v>3.639</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1048</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4135</v>
+        <v>0.2066</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5183</v>
+        <v>-0.2066</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0788</v>
+        <v>2.9561</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2562</v>
+        <v>2.946</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1774</v>
+        <v>0.0101</v>
       </c>
       <c r="G16" t="n">
         <v>0.9354</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5295</v>
+        <v>0.4068</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3583</v>
+        <v>0.048</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1712</v>
+        <v>0.3588</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5053</v>
+        <v>2.839</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5228</v>
+        <v>2.7296</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0174</v>
+        <v>0.1094</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4264</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0716</v>
+        <v>0.2621</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3864</v>
+        <v>-0.1795</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3148</v>
+        <v>0.4416</v>
       </c>
       <c r="V17" t="n">
         <v>4.5825</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7287</v>
+        <v>1.9907</v>
       </c>
       <c r="E18" t="n">
         <v>2.0881</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3595</v>
+        <v>-0.0974</v>
       </c>
       <c r="G18" t="n">
         <v>2.1007</v>
@@ -1858,13 +1858,13 @@
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4413</v>
+        <v>-0.1792</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3864</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0549</v>
+        <v>0.2072</v>
       </c>
       <c r="V18" t="n">
         <v>1.2277</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2732</v>
+        <v>1.8841</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9226</v>
+        <v>3.2329</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6494</v>
+        <v>-1.3488</v>
       </c>
       <c r="G19" t="n">
         <v>2.1461</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4522</v>
+        <v>0.1587</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3864</v>
+        <v>-0.0761</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0658</v>
+        <v>0.2348</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6138</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9296</v>
+        <v>1.0912</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5453</v>
+        <v>4.0563</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6157</v>
+        <v>-2.9651</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1102</v>
+        <v>1.8664</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2963</v>
+        <v>2.2349</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8138</v>
+        <v>-0.3685</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8143</v>
+        <v>3.7086</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4691</v>
+        <v>3.5458</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3451</v>
+        <v>0.1628</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7041</v>
+        <v>-1.8422</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1728</v>
+        <v>-1.3109</v>
       </c>
       <c r="O20" t="n">
         <v>-0.5313</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>0.105</v>
+        <v>-0.2965</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3036</v>
+        <v>-0.2001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4086</v>
+        <v>-0.0963</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7754</v>
+        <v>1.0694</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9529</v>
+        <v>1.6015</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1775</v>
+        <v>-0.5321</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8664</v>
+        <v>1.0072</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2349</v>
+        <v>0.3244</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3685</v>
+        <v>0.6827</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7086</v>
+        <v>3.5806</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5458</v>
+        <v>1.0147</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1628</v>
+        <v>2.5659</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8422</v>
+        <v>-2.5734</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3109</v>
+        <v>-0.6903</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5313</v>
+        <v>-1.8832</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6123</v>
+        <v>-0.2</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3036</v>
+        <v>-0.3106</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3087</v>
+        <v>0.1106</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4981</v>
+        <v>1.6487</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8686</v>
+        <v>-0.9137</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0072</v>
+        <v>1.1102</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3244</v>
+        <v>0.2963</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6827</v>
+        <v>0.8138</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5806</v>
+        <v>2.8143</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0147</v>
+        <v>1.4691</v>
       </c>
       <c r="L22" t="n">
-        <v>2.5659</v>
+        <v>1.3451</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5734</v>
+        <v>-1.7041</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6903</v>
+        <v>-1.1728</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8832</v>
+        <v>-0.5313</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.64</v>
+        <v>-0.0895</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.414</v>
+        <v>-0.2001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2259</v>
+        <v>0.1106</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.287</v>
+        <v>-0.2621</v>
       </c>
       <c r="E23" t="n">
         <v>-0.0345</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2525</v>
+        <v>-0.2276</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2483</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="T23" t="n">
         <v>0.1379</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9764</v>
+        <v>-0.9516</v>
       </c>
       <c r="E24" t="n">
         <v>-0.724</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2525</v>
+        <v>-0.2276</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9378</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="T24" t="n">
         <v>0.1379</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3752</v>
+        <v>-1.7959</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9026</v>
+        <v>-2.2129</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5274</v>
+        <v>0.417</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2622</v>
@@ -2404,13 +2404,13 @@
         <v>1.3515</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1034</v>
+        <v>0.6827</v>
       </c>
       <c r="T25" t="n">
-        <v>0.441</v>
+        <v>0.1307</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6624</v>
+        <v>0.552</v>
       </c>
       <c r="V25" t="n">
         <v>1.5559</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.4532</v>
+        <v>12.8321</v>
       </c>
       <c r="E26" t="n">
-        <v>21.2918</v>
+        <v>21.2917</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.838699999999999</v>
+        <v>-8.459600000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>6.930300000000001</v>
+        <v>6.930299999999999</v>
       </c>
       <c r="H26" t="n">
         <v>8.2752</v>
@@ -2482,13 +2482,13 @@
         <v>11.5845</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2752999999999999</v>
+        <v>1.1037</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6918</v>
+        <v>-0.6917</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4166000000000001</v>
+        <v>1.7955</v>
       </c>
       <c r="V26" t="n">
         <v>7.6944</v>
